--- a/12309365.xlsx
+++ b/12309365.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F4B36E-F5F9-4AFD-8119-2AC616473899}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C67AA20-21F1-4CC3-B42D-776B9E7E35B5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,6 +231,21 @@
   <si>
     <t>Spent some time coding and practiced new concepts.</t>
   </si>
+  <si>
+    <t>I need some extra time for other activities</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watching movies </t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scrolling reels </t>
+  </si>
 </sst>
 </file>
 
@@ -409,12 +424,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -898,74 +913,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12603423</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1145,13 +1160,13 @@
       <c r="M8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="18" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B9" s="14">
         <v>400</v>
@@ -1195,71 +1210,143 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46238</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>70</v>
+      </c>
+      <c r="D10" s="14">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14">
+        <v>80</v>
+      </c>
+      <c r="F10" s="14">
+        <v>480</v>
+      </c>
+      <c r="G10" s="14">
+        <v>7</v>
+      </c>
+      <c r="H10" s="14">
+        <v>200</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46239</v>
+      </c>
+      <c r="B11" s="14">
+        <v>460</v>
+      </c>
+      <c r="C11" s="14">
+        <v>50</v>
+      </c>
+      <c r="D11" s="14">
+        <v>100</v>
+      </c>
+      <c r="E11" s="14">
+        <v>50</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>120</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46240</v>
+      </c>
+      <c r="B12" s="14">
+        <v>500</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>100</v>
+      </c>
+      <c r="E12" s="14">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>130</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12309365.xlsx
+++ b/12309365.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C67AA20-21F1-4CC3-B42D-776B9E7E35B5}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFA93408-DFA4-4AC8-9E71-09D8AEA4B644}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t xml:space="preserve">scrolling reels </t>
+  </si>
+  <si>
+    <t xml:space="preserve">low </t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preaparing for networking ca </t>
   </si>
 </sst>
 </file>
@@ -528,6 +537,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1349,26 +1362,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46239</v>
+      </c>
+      <c r="B13" s="14">
+        <v>500</v>
+      </c>
+      <c r="C13" s="14">
+        <v>100</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>480</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
